--- a/DATA/DISENO_EXPERIMENTAL/estado_experimentos.xlsx
+++ b/DATA/DISENO_EXPERIMENTAL/estado_experimentos.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,16 +16,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +33,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,24 +41,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -425,86 +412,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Experimento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Variable_Objetivo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Tipo_Problema</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Dominio</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Ventana</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Horizonte</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Modelo</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Estado_Modelo</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Fecha_Ejecucion</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
@@ -531,11 +518,15 @@
           <t>Gestión Hídrica</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -552,23 +543,51 @@
           <t>Evaluar la capacidad del Framework para predecir el riesgo sanitario del agua.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>No apto para detectar objetivo</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.8462</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Línea base de clasificación IRCA; accuracy global aceptable, pero precision/recall nulos por desbalance o umbral.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Exp02</t>
+          <t>Exp01-V3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CALIDAD_AGUA</t>
+          <t>irca</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -581,11 +600,15 @@
           <t>Gestión Hídrica</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -594,36 +617,64 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Ejecutado</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Evaluar el comportamiento general de la calidad del recurso hídrico.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+          <t>Validar una versión mejorada del experimento IRCA con ajustes de preparación y evaluación.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Capacidad predictiva parcial</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.9226</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.5645</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.7292</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.6364</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Versión mejorada de clasificación IRCA; mayor recall y F1 frente a la línea base Exp01.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Exp03</t>
+          <t>Exp02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nivel_Minimo</t>
+          <t>CALIDAD_AGUA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Regresión</t>
+          <t>Clasificación</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -631,11 +682,15 @@
           <t>Gestión Hídrica</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>12</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -649,7 +704,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Validar la capacidad predictiva sobre la disponibilidad del recurso hídrico.</t>
+          <t>Evaluar el comportamiento general de la calidad del recurso hídrico.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -663,12 +718,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Exp04</t>
+          <t>Exp03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VolumenUtilDiarioMasa</t>
+          <t>Nivel_Minimo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -681,11 +736,15 @@
           <t>Gestión Hídrica</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -699,7 +758,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Validar la predicción del volumen útil disponible.</t>
+          <t>Validar la capacidad predictiva sobre la disponibilidad del recurso hídrico.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -713,12 +772,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Exp05</t>
+          <t>Exp04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DBO5</t>
+          <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -731,11 +790,15 @@
           <t>Gestión Hídrica</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>12</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -744,31 +807,43 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Ejecutado</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Evaluar contaminación orgánica.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>Validar la predicción del volumen útil disponible.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Regresión de VolumenUtilDiarioMasa con MAE=0.0824, RMSE=0.1470, MAPE=23.8944 y R2=0.7225.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Exp06</t>
+          <t>Exp05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DQO</t>
+          <t>DBO5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -781,11 +856,15 @@
           <t>Gestión Hídrica</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>12</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -799,7 +878,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Evaluar contaminación química.</t>
+          <t>Evaluar contaminación orgánica.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -813,12 +892,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Exp07</t>
+          <t>Exp06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Oxigeno_Disuelto</t>
+          <t>DQO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -831,11 +910,15 @@
           <t>Gestión Hídrica</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>12</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -849,7 +932,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Evaluar el estado ecológico del recurso.</t>
+          <t>Evaluar contaminación química.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -863,12 +946,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Exp08</t>
+          <t>Exp07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>Oxigeno_Disuelto</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -881,11 +964,15 @@
           <t>Gestión Hídrica</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>12</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -899,7 +986,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Evaluar el comportamiento fisicoquímico del agua.</t>
+          <t>Evaluar el estado ecológico del recurso.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -910,7 +997,61 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Exp08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Regresión</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Gestión Hídrica</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Evaluar el comportamiento fisicoquímico del agua.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/DATA/DISENO_EXPERIMENTAL/estado_experimentos.xlsx
+++ b/DATA/DISENO_EXPERIMENTAL/estado_experimentos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,75 +436,110 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Dominio</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Pregunta_Investigacion</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Objetivo_Experimento</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Variable_Objetivo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Tipo_Problema</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Dominio</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Numero_Predictores</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Registros_Disponibles</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cobertura_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Ventana</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Horizonte</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Modelo</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Objetivo</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Umbral_Cobertura_%</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Viabilidad</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Motivo_Viabilidad</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Estado_Modelo</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Fecha_Ejecucion</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
@@ -518,47 +553,74 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Gestión Hídrica</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>¿Es posible anticipar el riesgo sanitario del agua mediante información climática, hidrológica y de infraestructura?</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Evaluar la capacidad del Framework para predecir el IRCA y analizar factores asociados al riesgo sanitario del agua.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>irca</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Clasificación</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Gestión Hídrica</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="n">
+        <v>528</v>
+      </c>
+      <c r="I2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J2" t="n">
         <v>12</v>
       </c>
-      <c r="F2" t="n">
+      <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Ejecutado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Evaluar la capacidad del Framework para predecir el riesgo sanitario del agua.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>50</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Viable</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Cobertura de la variable objetivo suficiente para ejecutar el experimento.</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -568,47 +630,74 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CALIDAD_AGUA</t>
+          <t>Gestión Hídrica</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>¿Qué factores permiten anticipar el estado general de la calidad del agua?</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Evaluar la capacidad del Framework para predecir la calidad general del recurso hídrico.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Clasificación</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Gestión Hídrica</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="n">
+        <v>96</v>
+      </c>
+      <c r="I3" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="J3" t="n">
         <v>12</v>
       </c>
-      <c r="F3" t="n">
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Evaluar el comportamiento general de la calidad del recurso hídrico.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>50</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>No viable</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -618,47 +707,74 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Gestión Hídrica</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>¿Es posible anticipar la disminución del nivel mínimo del recurso hídrico?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Evaluar la capacidad predictiva del Framework sobre el nivel mínimo del recurso hídrico.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Nivel_Minimo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Gestión Hídrica</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="n">
+        <v>87</v>
+      </c>
+      <c r="I4" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="J4" t="n">
         <v>12</v>
       </c>
-      <c r="F4" t="n">
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Validar la capacidad predictiva sobre la disponibilidad del recurso hídrico.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>50</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>No viable</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -668,47 +784,74 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Gestión Hídrica</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>¿Qué variables permiten anticipar el volumen útil disponible del sistema?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Evaluar la capacidad del Framework para predecir el volumen útil disponible.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Gestión Hídrica</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>336</v>
+      </c>
+      <c r="I5" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="J5" t="n">
         <v>12</v>
       </c>
-      <c r="F5" t="n">
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Validar la predicción del volumen útil disponible.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>50</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Viable</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Cobertura de la variable objetivo suficiente para ejecutar el experimento.</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -718,47 +861,74 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DBO5</t>
+          <t>Gestión Hídrica</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>¿Es posible anticipar procesos de contaminación orgánica del agua?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Evaluar la capacidad predictiva del Framework sobre la Demanda Bioquímica de Oxígeno (DBO5).</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Gestión Hídrica</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="n">
+        <v>26</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="J6" t="n">
         <v>12</v>
       </c>
-      <c r="F6" t="n">
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Evaluar contaminación orgánica.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>No viable</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -768,47 +938,74 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DQO</t>
+          <t>Gestión Hídrica</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>¿Qué variables permiten anticipar la contaminación química del recurso hídrico?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Evaluar la capacidad predictiva del Framework sobre la Demanda Química de Oxígeno (DQO).</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Gestión Hídrica</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="n">
+        <v>49</v>
+      </c>
+      <c r="I7" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="J7" t="n">
         <v>12</v>
       </c>
-      <c r="F7" t="n">
+      <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Evaluar contaminación química.</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>50</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>No viable</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -818,47 +1015,74 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Oxigeno_Disuelto</t>
+          <t>Gestión Hídrica</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>¿Qué factores permiten anticipar cambios en el oxígeno disuelto del recurso hídrico?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Evaluar la capacidad predictiva del Framework sobre el Oxígeno Disuelto (OD).</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Gestión Hídrica</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" t="n">
+        <v>50</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="J8" t="n">
         <v>12</v>
       </c>
-      <c r="F8" t="n">
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Evaluar el estado ecológico del recurso.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>50</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>No viable</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -868,47 +1092,74 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Gestión Hídrica</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>¿Es posible anticipar cambios en el pH del agua?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Evaluar la capacidad predictiva del Framework sobre el pH.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>pH</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Gestión Hídrica</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" t="n">
+        <v>50</v>
+      </c>
+      <c r="I9" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="J9" t="n">
         <v>12</v>
       </c>
-      <c r="F9" t="n">
+      <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Evaluar el comportamiento fisicoquímico del agua.</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>50</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>No viable</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DATA/DISENO_EXPERIMENTAL/estado_experimentos.xlsx
+++ b/DATA/DISENO_EXPERIMENTAL/estado_experimentos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,90 +456,105 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Variable_Objetivo_Modelo</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Tipo_Problema</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Numero_Predictores</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Registros_Disponibles</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Cobertura_%</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Registros_Objetivo_Modelo</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Cobertura_Objetivo_Modelo_%</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Ventana</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Horizonte</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Modelo</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Umbral_Cobertura_%</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Viabilidad</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Motivo_Viabilidad</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Estado_Modelo</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Fecha_Ejecucion</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
@@ -573,54 +588,65 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>nivel_de_riesgo</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>Clasificación</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>9</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>528</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>100</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
+        <v>528</v>
+      </c>
+      <c r="L2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M2" t="n">
         <v>12</v>
       </c>
-      <c r="K2" t="n">
+      <c r="N2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>50</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Viable</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Cobertura de la variable objetivo suficiente para ejecutar el experimento.</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -650,54 +676,65 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Clasificación</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>10</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>96</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>18.18</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
+        <v>96</v>
+      </c>
+      <c r="L3" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="M3" t="n">
         <v>12</v>
       </c>
-      <c r="K3" t="n">
+      <c r="N3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
         <v>50</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>No viable</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -727,54 +764,65 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>10</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>87</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>16.48</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
+        <v>87</v>
+      </c>
+      <c r="L4" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="M4" t="n">
         <v>12</v>
       </c>
-      <c r="K4" t="n">
+      <c r="N4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="N4" t="n">
+      <c r="Q4" t="n">
         <v>50</v>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>No viable</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -804,54 +852,65 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>9</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>336</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>63.64</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
+        <v>336</v>
+      </c>
+      <c r="L5" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="M5" t="n">
         <v>12</v>
       </c>
-      <c r="K5" t="n">
+      <c r="N5" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="N5" t="n">
+      <c r="Q5" t="n">
         <v>50</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Viable</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Cobertura de la variable objetivo suficiente para ejecutar el experimento.</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -881,54 +940,65 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>10</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>26</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>4.92</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
+        <v>26</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="M6" t="n">
         <v>12</v>
       </c>
-      <c r="K6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
         <v>50</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>No viable</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -958,54 +1028,65 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>10</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>49</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>9.279999999999999</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
+        <v>49</v>
+      </c>
+      <c r="L7" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="M7" t="n">
         <v>12</v>
       </c>
-      <c r="K7" t="n">
+      <c r="N7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="N7" t="n">
+      <c r="Q7" t="n">
         <v>50</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>No viable</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1035,54 +1116,65 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>10</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>50</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>9.470000000000001</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
+        <v>50</v>
+      </c>
+      <c r="L8" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="M8" t="n">
         <v>12</v>
       </c>
-      <c r="K8" t="n">
+      <c r="N8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="N8" t="n">
+      <c r="Q8" t="n">
         <v>50</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>No viable</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1112,54 +1204,65 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>10</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>50</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>9.470000000000001</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
+        <v>50</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="M9" t="n">
         <v>12</v>
       </c>
-      <c r="K9" t="n">
+      <c r="N9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="N9" t="n">
+      <c r="Q9" t="n">
         <v>50</v>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>No viable</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
